--- a/submission/Pavo_Cloud_3Yr_Financial_Model.xlsx
+++ b/submission/Pavo_Cloud_3Yr_Financial_Model.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="170" formatCode="0.0000&quot; s&quot;"/>
     <numFmt numFmtId="171" formatCode="0.000&quot; s&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="$#,##0.0000"/>
+    <numFmt numFmtId="173" formatCode="$#,##0.000000"/>
     <numFmt numFmtId="174" formatCode="$0.000000"/>
     <numFmt numFmtId="175" formatCode="0.000000"/>
   </numFmts>
@@ -309,7 +309,7 @@
     <xf numFmtId="174" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>

--- a/submission/Pavo_Cloud_3Yr_Financial_Model.xlsx
+++ b/submission/Pavo_Cloud_3Yr_Financial_Model.xlsx
@@ -730,8 +730,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,11 +769,6 @@
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Basis / source</t>
         </is>
@@ -1365,8 +1359,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1405,11 +1398,6 @@
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -2687,9 +2675,9 @@
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2719,19 +2707,11 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Unit cost</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Cost per auth</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
           <t>How it was measured</t>
         </is>
       </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
